--- a/Excel/Ejercicios/semana 3/13- Caso_integrado_Excel_ALUMNADO.xlsx
+++ b/Excel/Ejercicios/semana 3/13- Caso_integrado_Excel_ALUMNADO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Esquema del día\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\Excel-PowerBI\Excel\Ejercicios\semana 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3068B7012F05AFCD1E23C9FE09C2F1D55E04789A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB1F54F-6A04-48E2-94D4-2E92BDCA4F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guía del ejercicio" sheetId="1" r:id="rId1"/>
@@ -1800,13 +1800,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2028,50 +2028,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="23.95" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="23.95" customHeight="1">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
@@ -2239,16 +2239,16 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15264,38 +15264,7 @@
       <c r="G31" s="10"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" sqref="B2:B31" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Asturias,Galicia,Cantabria,Castilla y León,Madrid"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="C2:C31" xr:uid="{00000000-0002-0000-0400-000001000000}">
-      <formula1>"Tienda,Web,Empresa"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="D2:D31" xr:uid="{00000000-0002-0000-0400-000002000000}">
-      <formula1>"Entregado,Pendiente,Cancelado"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" sqref="F2:F31" xr:uid="{00000000-0002-0000-0400-000004000000}">
-      <formula1>1</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" sqref="G2:G31" xr:uid="{00000000-0002-0000-0400-000005000000}">
-      <formula1>0</formula1>
-      <formula2>0.3</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0400-000003000000}">
-          <x14:formula1>
-            <xm:f>Catálogo!$A$2:$A$26</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E31</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -15309,12 +15278,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.45">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>537</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
@@ -25106,12 +25075,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
